--- a/output/audit.xlsx
+++ b/output/audit.xlsx
@@ -451,10 +451,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -615,140 +615,240 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attributed Leads</t>
+          <t>Paid Leads</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>390</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unattributed Leads</t>
+          <t>Unpaid Leads</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Total Sales</t>
+          <t>Paid Funnel %</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>41</v>
+        <v>84.95370370370371</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attributed Sales</t>
+          <t>Unpaid Funnel %</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32</v>
+        <v>15.0462962962963</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unattributed Sales</t>
+          <t>Attributed Leads</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
+          <t>Unattributed Leads</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>279600</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Attributed Revenue</t>
+          <t>Total Sales</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>216690</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Raw Meta Spend</t>
+          <t>Attributed Sales</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24853.19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attributed Spend</t>
+          <t>Unattributed Sales</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24853.19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unallocated Spend</t>
+          <t>Per Sale Value</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>6819.512195121952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Profit</t>
+          <t>Attributed Per Sale Value</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>191836.81</v>
+        <v>6771.5625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ROAS</t>
+          <t>Registration Amount</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.718800282780601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ROI</t>
+          <t>Sales Revenue</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>771.88002827806</v>
+        <v>279600</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Registration Revenue</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>279600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Attributed Revenue</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>216690</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unattributed Revenue</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>62910</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>24853.19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>24853.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>191836.81</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8.718800282780601</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>771.88002827806</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>CAC</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B37" t="n">
         <v>776.6621875000001</v>
       </c>
     </row>
@@ -1375,7 +1475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1501,7 @@
     <col width="25" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="29" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1519,6 +1620,11 @@
           <t>Results (initial) indicator</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>source_file_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -1599,6 +1705,9 @@
       <c r="W2" t="n">
         <v/>
       </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1679,6 +1788,9 @@
       <c r="W3" t="n">
         <v/>
       </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1764,6 +1876,9 @@
       <c r="W4" t="n">
         <v/>
       </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1848,6 +1963,9 @@
       </c>
       <c r="W5" t="n">
         <v/>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2110,10 +2228,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="D9" t="n">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3375,8 +3493,10 @@
           <t>pratibha3226@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9360302396</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9360302396</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3705,8 +3825,10 @@
           <t>deepthi.darshan@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>9480516146</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9480516146</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4064,8 +4186,10 @@
           <t>drshailjapande@gmail.com</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>9891494973</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9891494973</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4423,8 +4547,10 @@
           <t>logeshwari.cloud@gmail.com</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>8748866501</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8748866501</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4782,8 +4908,10 @@
           <t>niyatif@gmail.com</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>8899202416</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8899202416</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -5141,8 +5269,10 @@
           <t>kiran_puthran@hotmail.com</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>9619191127</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9619191127</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5500,8 +5630,10 @@
           <t>arpipatel1@gmail.com</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>9033036061</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9033036061</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -5850,8 +5982,10 @@
           <t>priyankavpatil8@gmail.com</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>9049835216</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9049835216</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6209,8 +6343,10 @@
           <t>joycerosy.jr@gmail.com</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>9916260796</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9916260796</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6568,8 +6704,10 @@
           <t>salvi.mayura1976@gmail.com</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>9923330110</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9923330110</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6927,8 +7065,10 @@
           <t>mailtoshree07@gmail.com</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>9538558933</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>9538558933</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7286,8 +7426,10 @@
           <t>vaibhavi2006@gmail.com</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>9689531850</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9689531850</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7645,8 +7787,10 @@
           <t>pritikajohri@gmail.com</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>9962210323</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9962210323</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -8004,8 +8148,10 @@
           <t>chillampallymanisha@gmail.com</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>9059370850</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9059370850</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -8363,8 +8509,10 @@
           <t>kudtarkar.archana.25@gmail.com</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>8291210037</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8291210037</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -8722,8 +8870,10 @@
           <t>yvumadevi@gmail.com</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>8446610535</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8446610535</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9081,8 +9231,10 @@
           <t>singhla.aashvi5@gmail.com</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>8699236275</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8699236275</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9411,8 +9563,10 @@
           <t>anitabose@gmail.com</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>9873197747</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9873197747</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9741,8 +9895,10 @@
           <t>jelsia293@gmail.com</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>7708592813</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7708592813</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -10071,8 +10227,10 @@
           <t>vkhamborkar@gmail.com</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>8793211595</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8793211595</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -10430,8 +10588,10 @@
           <t>dr.knisha@gmail.com</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>9731574492</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>9731574492</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10762,8 +10922,10 @@
           <t>diarypreet@gmail.com</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>8951156002</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>8951156002</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -11121,8 +11283,10 @@
           <t>nikitavikas2018@gmail.com</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>9686622672</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>9686622672</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11480,8 +11644,10 @@
           <t>monicagosavi01@gmail.com</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>9769347947</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>9769347947</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -11839,8 +12005,10 @@
           <t>gunaswetha21@gmail.com</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>9148858262</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9148858262</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -12198,8 +12366,10 @@
           <t>manisharabade13@gmail.com</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>9403651740</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9403651740</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -12557,8 +12727,10 @@
           <t>minakshi283@gmail.com</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>8527655899</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>8527655899</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -12887,8 +13059,10 @@
           <t>mnsabharadwaj@gmail.com</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>9901801703</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>9901801703</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -13246,8 +13420,10 @@
           <t>mohinit1190@gmail.com</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>9167639490</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>9167639490</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -13610,8 +13786,10 @@
           <t>nivedhaharibabu@gmail.com</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>9791063154</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>9791063154</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13942,8 +14120,10 @@
           <t>puipath10@gmail.com</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>9845673844</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>9845673844</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -14301,8 +14481,10 @@
           <t>neelam.1903@gmail.com</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>9911703398</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>9911703398</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -14660,8 +14842,10 @@
           <t>bhagvatichoudhary03@gmail.com</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>9673313650</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>9673313650</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -15019,8 +15203,10 @@
           <t>ksgscse@gmail.com</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>9444702450</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>9444702450</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -15378,8 +15564,10 @@
           <t>sakshipahwa2018@gmail.com</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>9910744885</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>9910744885</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -15708,8 +15896,10 @@
           <t>k11.rashmi@gmail.com</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>7406703335</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7406703335</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -16067,8 +16257,10 @@
           <t>latha.kn1811@gmail.com</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>9538175099</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>9538175099</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -16426,8 +16618,10 @@
           <t>nehaconnect123@gmail.com</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>9769223732</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9769223732</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -16785,8 +16979,10 @@
           <t>nelsonsharon22@yahoo.com</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>7356597993</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7356597993</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -17144,8 +17340,10 @@
           <t>pillutllahimabindu@gmail.com</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>8121749890</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8121749890</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -17474,8 +17672,10 @@
           <t>reachdelphine@gmail.com</t>
         </is>
       </c>
-      <c r="C42" t="n">
-        <v>9916725925</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9916725925</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -17833,16 +18033,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -17929,20 +18129,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="3" t="n">
+        <v>47.36842105263158</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>62910</v>
@@ -17986,20 +18182,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>117</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="3" t="n">
+        <v>7.692307692307693</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>62910</v>
@@ -18043,20 +18235,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="3" t="n">
+        <v>6.024096385542169</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>34950</v>
@@ -18100,20 +18288,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G5" s="3" t="n">
+        <v>5.970149253731343</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>27960</v>
@@ -18157,20 +18341,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G6" s="3" t="n">
+        <v>22.22222222222222</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20970</v>
@@ -18214,20 +18394,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" s="3" t="n">
+        <v>4.6875</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>20970</v>
@@ -18271,20 +18447,16 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G8" s="3" t="n">
+        <v>16.66666666666666</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>6990</v>
@@ -18328,20 +18500,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G9" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>6990</v>
@@ -18385,20 +18553,16 @@
         <v>13296.16</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2216.026666666667</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="3" t="n">
+        <v>16.66666666666666</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>6990</v>
@@ -18436,20 +18600,16 @@
         <v>11557.03</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1651.004285714286</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G11" s="3" t="n">
+        <v>14.28571428571428</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>6990</v>
@@ -18487,20 +18647,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G12" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6990</v>
@@ -18544,20 +18700,16 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G13" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>6990</v>
@@ -18601,20 +18753,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G14" s="3" t="n">
+        <v>4.166666666666666</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>6990</v>
@@ -18646,7 +18794,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 04 /07&lt;&gt; cbo &lt;&gt; rs. 199</t>
+          <t>fb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -18658,20 +18806,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>0</v>
@@ -18703,55 +18847,112 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>foremost leads &lt;&gt; 04 /07&lt;&gt; cbo &lt;&gt; rs. 199</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>foremost leads &lt;&gt; 06 /07&lt;&gt; cbo &lt;&gt; 199</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -18768,16 +18969,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -18868,20 +19069,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="3" t="n">
+        <v>47.36842105263158</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>62910</v>
@@ -18913,7 +19110,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 04 /07&lt;&gt; cbo &lt;&gt; rs. 199 &gt; </t>
+          <t>fb &gt; facebook_desktop_feed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18925,20 +19122,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -18970,7 +19163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 06 /07&lt;&gt; cbo &lt;&gt; 199 &gt; </t>
+          <t>fb &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18982,20 +19175,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -19027,7 +19216,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &amp; moms – copy 2</t>
+          <t>fb &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19039,52 +19228,48 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; abo &lt;&gt; sales – copy &gt; parents</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -19096,52 +19281,48 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &amp; moms – copy 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19153,26 +19334,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>33.33333333333333</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -19198,7 +19375,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &amp; mothers – copy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19210,52 +19387,48 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>20970</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>20970</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; housewives and mothers</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives and mothers – copy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -19267,52 +19440,48 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>13980</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>13980</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; job interests (women only)</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; sales – copy &gt; parents</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -19324,20 +19493,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G10" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>6990</v>
@@ -19369,7 +19534,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19381,26 +19546,22 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11.11111111111111</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -19426,7 +19587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives &amp; moms – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives &amp; mothers</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -19438,52 +19599,48 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>55920</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>55920</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives and mothers</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19495,52 +19652,48 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &amp; moms – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -19552,26 +19705,22 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>14.28571428571428</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6990</v>
+        <v>20970</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>6990</v>
+        <v>20970</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -19597,7 +19746,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests (women only) – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; housewives and mothers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -19609,26 +19758,22 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>4.761904761904762</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -19654,7 +19799,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests women only – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; job interests (women only)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -19666,20 +19811,16 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G16" s="3" t="n">
+        <v>4.545454545454546</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>6990</v>
@@ -19711,7 +19852,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -19720,55 +19861,51 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13296.16</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>3.225806451612903</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives &amp; moms – copy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -19780,46 +19917,48 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
+        <v>86</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>9.302325581395349</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>55920</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>55920</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>-6306.16</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0.5257156953586599</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>-47.428430464134</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>13296.16</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; wn &lt;&gt; cbo &gt; </t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -19828,55 +19967,51 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>11557.03</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; wn &lt;&gt; cbo &gt; parents</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &amp; moms – copy 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -19888,46 +20023,48 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>6990</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <v>-4567.030000000001</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0.6048266725966792</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>-39.51733274033208</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>11557.03</v>
+      <c r="I20" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ig &gt; instagram_feed</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &amp; mothers – copy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -19939,20 +20076,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>0</v>
@@ -19984,7 +20117,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ig &gt; instagram_stories</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives and mothers – copy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -19996,52 +20129,48 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ig &gt; social</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests (women only) – copy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -20053,26 +20182,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>6.25</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -20098,7 +20223,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>linkedin &gt; organic</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests women only – copy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -20110,20 +20235,16 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G24" s="3" t="n">
+        <v>7.692307692307693</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>6990</v>
@@ -20155,7 +20276,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>major_ rm_ test_ wn_ foremost leads &lt;&gt; 27-07 &gt; housewives &amp; moms – copy 2</t>
+          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -20164,103 +20285,560 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>2216.026666666667</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2216.026666666667</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G25" s="3" t="n">
+        <v>100</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>6990</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="I25" s="6" t="n">
+        <v>-6306.16</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.5257156953586599</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>-47.428430464134</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>13296.16</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open – copy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open – copy 4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>8864.106666666667</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; wn &lt;&gt; cbo &gt; parents</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>11557.03</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1651.004285714286</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>-4567.030000000001</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.6048266725966792</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>-39.51733274033208</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>11557.03</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ig &gt; instagram_feed</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ig &gt; instagram_reels</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ig &gt; instagram_stories</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ig &gt; social</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>13980</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>13980</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>linkedin &gt; organic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>major_ rm_ test_ wn_ foremost leads &lt;&gt; 27-07 &gt; housewives &amp; moms – copy 2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>{{campaign.name}} &gt; {{adset.name}}</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>24</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -20277,16 +20855,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -20377,20 +20955,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G2" s="3" t="n">
+        <v>47.36842105263158</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>62910</v>
@@ -20422,7 +20996,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 04 /07&lt;&gt; cbo &lt;&gt; rs. 199 &gt;  &gt; </t>
+          <t>fb &gt; facebook_desktop_feed &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20434,20 +21008,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
@@ -20479,7 +21049,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; 06 /07&lt;&gt; cbo &lt;&gt; 199 &gt;  &gt; </t>
+          <t>fb &gt; facebook_mobile_reels &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20491,20 +21061,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -20536,7 +21102,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &amp; moms – copy 2 &gt; confused about – copy 2</t>
+          <t>fb &gt; facebook_stories &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20548,52 +21114,48 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; abo &lt;&gt; sales – copy &gt; parents &gt; purple success stories video – copy</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20605,52 +21167,48 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &amp; moms – copy 2 &gt; confused about – copy 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20662,26 +21220,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>33.33333333333333</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -20707,7 +21261,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only &gt; ad with text strip &lt;&gt; krishna – copy</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives &amp; mothers – copy &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20719,52 +21273,48 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>13980</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>13980</v>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only &gt; if you're a women on career break due to maternity due to marriage</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; master &lt;&gt; scaled &gt; housewives and mothers – copy &gt; image ad | there's a way back to work after career break</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20776,52 +21326,48 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; housewives and mothers &gt; image ad | whiteboard | iceberg | women on career break</t>
+          <t>foremost leads &lt;&gt; abo &lt;&gt; sales – copy &gt; parents &gt; purple success stories video – copy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20833,26 +21379,22 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -20878,7 +21420,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; job interests (women only) &gt; image ad | whiteboard | iceberg | women on career break – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20890,26 +21432,22 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11.11111111111111</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -20935,7 +21473,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives &gt; confused about – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives &amp; mothers &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20947,52 +21485,48 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
+        <v>43</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives &amp; moms – copy &gt; confused about – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; housewives and mothers &gt; if you're a women career break you don;t have any offer letter and no interview calls</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21004,52 +21538,48 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>55920</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>55920</v>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &gt; confused about – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only &gt; ad with text strip &lt;&gt; krishna – copy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -21061,26 +21591,22 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>15.38461538461539</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>6990</v>
+        <v>13980</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -21106,7 +21632,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &amp; moms – copy 2 &gt; confused about – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only &gt; if you're a women on career break due to maternity due to marriage</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -21118,20 +21644,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G15" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>6990</v>
@@ -21163,7 +21685,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests (women only) – copy &gt; image ad | women on career break are getting hired again – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; desk format | faceless &gt; job interests women only &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -21175,52 +21697,48 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests women only – copy &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; housewives and mothers &gt; image ad | there's a way back to work after career break</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21232,52 +21750,48 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; housewives and mothers &gt; image ad | whiteboard | iceberg | women on career break</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -21286,55 +21800,51 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13296.16</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>8.695652173913043</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>13980</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>13980</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open &gt; women on a career break : get a job again &lt;&gt; orange bg &lt;&gt; image &lt;&gt;</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; housewives and mothers &gt; image ad | women on career break are getting hired again</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -21346,35 +21856,37 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>-6306.16</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>0.5257156953586599</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>-47.428430464134</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>13296.16</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -21385,7 +21897,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">foremost leads &lt;&gt; wn &lt;&gt; cbo &gt;  &gt; </t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; job interests (women only) &gt; image ad | whiteboard | iceberg | women on career break – copy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21394,55 +21906,51 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>11557.03</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>5.263157894736842</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; wn &lt;&gt; cbo &gt; parents &gt; women on a career break : get a job again &lt;&gt; orange bg &lt;&gt; image &lt;&gt; – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; image ads | ai generated &gt; job interests (women only) &gt; image ad | women on career break are getting hired again – copy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21454,35 +21962,37 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>-4567.030000000001</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>0.6048266725966792</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>-39.51733274033208</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>11557.03</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -21493,7 +22003,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ig &gt; instagram_feed &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives &gt; confused about – copy 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21505,52 +22015,48 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="3" t="n">
+        <v>3.225806451612903</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ig &gt; instagram_stories &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; master campaign &gt; housewives &amp; moms – copy &gt; confused about – copy 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21562,26 +22068,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>86</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>9.302325581395349</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>6990</v>
+        <v>55920</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>6990</v>
+        <v>55920</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -21607,7 +22109,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ig &gt; social &gt; link_in_bio</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &gt; confused about – copy 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21619,26 +22121,22 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>33.33333333333333</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>13980</v>
+        <v>6990</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -21664,7 +22162,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">linkedin &gt; organic &gt; </t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &gt; how ro comeback after career break red yellow image – copy 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21676,52 +22174,48 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>major_ rm_ test_ wn_ foremost leads &lt;&gt; 27-07 &gt; housewives &amp; moms – copy 2 &gt; confused about – copy 2</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -21733,52 +22227,48 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>6990</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>6990</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; image ad | women on career break are getting hired again</t>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &amp; moms – copy 2 &gt; confused about – copy 2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -21790,20 +22280,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G27" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>6990</v>
@@ -21829,6 +22315,1001 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives &amp; mothers – copy &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; housewives and mothers – copy &gt; image ad | women on career break are getting hired again</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests (women only) – copy &gt; image ad | whiteboard | iceberg | women on career break – copy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests (women only) – copy &gt; image ad | women on career break are getting hired again – copy</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>7.142857142857142</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests women only – copy &gt; if you're a women on career break due to maternity due to marriage</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; master campaign &lt;&gt; abo &gt; job interests women only – copy &gt; if you;re a women on career break with 2 5 6 8 10 15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open &gt; women on a career break : get a job again &lt;&gt; orange bg &lt;&gt; image &lt;&gt;</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>-6306.16</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.5257156953586599</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>-47.428430464134</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>13296.16</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open – copy &gt; nobody absolutely nobody &lt;&gt; white plain card &lt;&gt; image</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; test campaign &lt;&gt; cbo &lt;&gt; &gt; open – copy 4 &gt; women restarts her career after a 10 year break</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>8864.106666666667</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2216.026666666667</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; wn &lt;&gt; cbo &gt; parents &gt; nobody absolutely nobody &lt;&gt; white plain card &lt;&gt; image – copy</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>4953.012857142857</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1651.004285714286</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>foremost leads &lt;&gt; wn &lt;&gt; cbo &gt; parents &gt; women on a career break : get a job again &lt;&gt; orange bg &lt;&gt; image &lt;&gt; – copy</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>6604.017142857143</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1651.004285714286</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>-4567.030000000001</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>0.6048266725966792</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>-39.51733274033208</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>11557.03</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ig &gt; instagram_feed &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ig &gt; instagram_reels &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ig &gt; instagram_stories &gt; if you have ever asked yourself video-adset: india testing sales ad set</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ig &gt; social &gt; link_in_bio</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>13980</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>13980</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linkedin &gt; organic &gt; </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>major_ rm_ test_ wn_ foremost leads &lt;&gt; 27-07 &gt; housewives &amp; moms – copy 2 &gt; confused about – copy 2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; image ad | women on career break are getting hired again</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>23</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -22591,8 +24072,10 @@
           <t>pratibha3226@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9360302396</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9360302396</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -22921,8 +24404,10 @@
           <t>singhla.aashvi5@gmail.com</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>8699236275</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8699236275</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -23251,8 +24736,10 @@
           <t>anitabose@gmail.com</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>9873197747</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9873197747</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -23581,8 +25068,10 @@
           <t>jelsia293@gmail.com</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>7708592813</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7708592813</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -23911,8 +25400,10 @@
           <t>dr.knisha@gmail.com</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>9731574492</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9731574492</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -24243,8 +25734,10 @@
           <t>minakshi283@gmail.com</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>8527655899</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8527655899</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -24573,8 +26066,10 @@
           <t>nivedhaharibabu@gmail.com</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>9791063154</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9791063154</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -24905,8 +26400,10 @@
           <t>sakshipahwa2018@gmail.com</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>9910744885</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9910744885</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -25235,8 +26732,10 @@
           <t>pillutllahimabindu@gmail.com</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>8121749890</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8121749890</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
